--- a/workspace/core4d/report/0908/paper_cmp_v2/method_comparison.xlsx
+++ b/workspace/core4d/report/0908/paper_cmp_v2/method_comparison.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,40 +463,60 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>OmniRetarget mean</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>OmniRetarget std</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>OmniRetarget worst</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>OmniRetarget n</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>SBTO mean</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>SBTO std</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>SBTO worst</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>SBTO n</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>GMR mean</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>GMR std</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>GMR worst</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>GMR n</t>
         </is>
@@ -526,29 +546,41 @@
         <v>50</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3437164730137199</v>
+        <v>0.218551157130546</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1449838549765821</v>
+        <v>0.246869177840298</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03773584905660377</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>50</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0021606</v>
+        <v>0.3437164730137199</v>
       </c>
       <c r="L2" t="n">
-        <v>0.005200477828046188</v>
+        <v>0.1449838549765821</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>0.03773584905660377</v>
       </c>
       <c r="N2" t="n">
         <v>50</v>
       </c>
+      <c r="O2" t="n">
+        <v>0.0021606</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.005200477828046188</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -574,29 +606,41 @@
         <v>50</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3658862871531136</v>
+        <v>0.4463240233956368</v>
       </c>
       <c r="H3" t="n">
-        <v>0.158528979001597</v>
+        <v>0.2502034026841141</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7340425531914894</v>
+        <v>0.8776595744680851</v>
       </c>
       <c r="J3" t="n">
         <v>50</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0464534</v>
+        <v>0.3658862871531136</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1275241399047255</v>
+        <v>0.158528979001597</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6137899999999999</v>
+        <v>0.7340425531914894</v>
       </c>
       <c r="N3" t="n">
         <v>50</v>
       </c>
+      <c r="O3" t="n">
+        <v>0.0464534</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.1275241399047255</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.6137899999999999</v>
+      </c>
+      <c r="R3" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -622,29 +666,41 @@
         <v>50</v>
       </c>
       <c r="G4" t="n">
-        <v>25.35676787326028</v>
+        <v>21.61024762445779</v>
       </c>
       <c r="H4" t="n">
-        <v>14.8225168356933</v>
+        <v>20.33300135968454</v>
       </c>
       <c r="I4" t="n">
-        <v>72.21469964075384</v>
+        <v>97.72935427813795</v>
       </c>
       <c r="J4" t="n">
         <v>50</v>
       </c>
       <c r="K4" t="n">
-        <v>23.513014</v>
+        <v>25.35676787326028</v>
       </c>
       <c r="L4" t="n">
-        <v>58.5437307384551</v>
+        <v>14.8225168356933</v>
       </c>
       <c r="M4" t="n">
-        <v>256.4209</v>
+        <v>72.21469964075384</v>
       </c>
       <c r="N4" t="n">
         <v>50</v>
       </c>
+      <c r="O4" t="n">
+        <v>23.513014</v>
+      </c>
+      <c r="P4" t="n">
+        <v>58.5437307384551</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>256.4209</v>
+      </c>
+      <c r="R4" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -670,29 +726,41 @@
         <v>50</v>
       </c>
       <c r="G5" t="n">
-        <v>1.76318528336824</v>
+        <v>2.769196137098584</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4217479479063979</v>
+        <v>1.178684090367079</v>
       </c>
       <c r="I5" t="n">
-        <v>3.240170629016954</v>
+        <v>5.697912136969935</v>
       </c>
       <c r="J5" t="n">
         <v>50</v>
       </c>
       <c r="K5" t="n">
-        <v>1.8338738</v>
+        <v>1.76318528336824</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7875529940921817</v>
+        <v>0.4217479479063979</v>
       </c>
       <c r="M5" t="n">
-        <v>3.90039</v>
+        <v>3.240170629016954</v>
       </c>
       <c r="N5" t="n">
         <v>50</v>
       </c>
+      <c r="O5" t="n">
+        <v>1.8338738</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.7875529940921817</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.90039</v>
+      </c>
+      <c r="R5" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -718,27 +786,39 @@
         <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>1.19965045037334</v>
+        <v>1.330331309747668</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4808434140309802</v>
+        <v>0.475249530333969</v>
       </c>
       <c r="I6" t="n">
-        <v>2.376978856501543</v>
+        <v>2.404735224195784</v>
       </c>
       <c r="J6" t="n">
         <v>50</v>
       </c>
       <c r="K6" t="n">
+        <v>1.19965045037334</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.4808434140309802</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.376978856501543</v>
+      </c>
+      <c r="N6" t="n">
+        <v>50</v>
+      </c>
+      <c r="O6" t="n">
         <v>0.9706988</v>
       </c>
-      <c r="L6" t="n">
+      <c r="P6" t="n">
         <v>0.5090938303795873</v>
       </c>
-      <c r="M6" t="n">
+      <c r="Q6" t="n">
         <v>2.21639</v>
       </c>
-      <c r="N6" t="n">
+      <c r="R6" t="n">
         <v>50</v>
       </c>
     </row>
@@ -753,7 +833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -774,70 +854,95 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Phys. contact@5mm·OmniRetarget</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Phys. contact@5mm·SBTO</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Phys. contact@5mm·GMR</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Phys. penetration@5mm·SPIDER-CEM</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Phys. penetration@5mm·OmniRetarget</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Phys. penetration@5mm·SBTO</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Phys. penetration@5mm·GMR</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Max phys penetration (mm)·SPIDER-CEM</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Max phys penetration (mm)·OmniRetarget</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Max phys penetration (mm)·SBTO</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Max phys penetration (mm)·GMR</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Obj speed max (m/s)·SPIDER-CEM</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Obj speed max (m/s)·OmniRetarget</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Obj speed max (m/s)·SBTO</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Obj speed max (m/s)·GMR</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Foot slip max (m)·SPIDER-CEM</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Foot slip max (m)·OmniRetarget</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Foot slip max (m)·SBTO</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Foot slip max (m)·GMR</t>
         </is>
@@ -856,45 +961,60 @@
         <v>0.7487590983120475</v>
       </c>
       <c r="D2" t="n">
+        <v>0.01711732136890841</v>
+      </c>
+      <c r="E2" t="n">
         <v>0.3828879554354274</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
       <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
         <v>0.05838912472355322</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
+        <v>0.6038786468974432</v>
+      </c>
+      <c r="I2" t="n">
         <v>0.2246509714091796</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>0.008546666666666666</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>9.113735212967883</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
+        <v>17.19731267265839</v>
+      </c>
+      <c r="M2" t="n">
         <v>16.50273811751878</v>
       </c>
-      <c r="K2" t="n">
+      <c r="N2" t="n">
         <v>7.488230000000001</v>
       </c>
-      <c r="L2" t="n">
+      <c r="O2" t="n">
         <v>1.138250376865439</v>
       </c>
-      <c r="M2" t="n">
+      <c r="P2" t="n">
+        <v>1.947107374829001</v>
+      </c>
+      <c r="Q2" t="n">
         <v>1.485020026744754</v>
       </c>
-      <c r="N2" t="n">
+      <c r="R2" t="n">
         <v>1.29233</v>
       </c>
-      <c r="O2" t="n">
+      <c r="S2" t="n">
         <v>0.8322767719960443</v>
       </c>
-      <c r="P2" t="n">
+      <c r="T2" t="n">
+        <v>1.227473574977549</v>
+      </c>
+      <c r="U2" t="n">
         <v>1.210170880783132</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="V2" t="n">
         <v>0.8454483333333332</v>
       </c>
     </row>
@@ -911,45 +1031,60 @@
         <v>0.6236230375574637</v>
       </c>
       <c r="D3" t="n">
+        <v>0.1520730332205742</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.2804449648711944</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
       <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
         <v>0.04078071595610722</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
+        <v>0.5147380052938607</v>
+      </c>
+      <c r="I3" t="n">
         <v>0.3587841252709035</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
         <v>7.224821049945025</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
+        <v>13.21811214861389</v>
+      </c>
+      <c r="M3" t="n">
         <v>38.02845336209489</v>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
         <v>1.363390452576342</v>
       </c>
-      <c r="M3" t="n">
+      <c r="P3" t="n">
+        <v>3.506201264796614</v>
+      </c>
+      <c r="Q3" t="n">
         <v>1.887988885533839</v>
       </c>
-      <c r="N3" t="n">
+      <c r="R3" t="n">
         <v>2.39661</v>
       </c>
-      <c r="O3" t="n">
+      <c r="S3" t="n">
         <v>1.101427654510164</v>
       </c>
-      <c r="P3" t="n">
+      <c r="T3" t="n">
+        <v>1.128478487248786</v>
+      </c>
+      <c r="U3" t="n">
         <v>1.18645352174259</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="V3" t="n">
         <v>0.7735799999999999</v>
       </c>
     </row>
@@ -966,45 +1101,60 @@
         <v>0.677937214366056</v>
       </c>
       <c r="D4" t="n">
+        <v>0.5167993133037896</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.3467073918537002</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>0.0007877777777777778</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>0.0845306732731172</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
+        <v>0.2846709599278018</v>
+      </c>
+      <c r="I4" t="n">
         <v>0.3801102961373037</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>0.11154</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>15.54211991981921</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
+        <v>8.469500307982466</v>
+      </c>
+      <c r="M4" t="n">
         <v>40.04776490962079</v>
       </c>
-      <c r="K4" t="n">
+      <c r="N4" t="n">
         <v>40.58301888888889</v>
       </c>
-      <c r="L4" t="n">
+      <c r="O4" t="n">
         <v>1.329134601529297</v>
       </c>
-      <c r="M4" t="n">
+      <c r="P4" t="n">
+        <v>3.356184355431723</v>
+      </c>
+      <c r="Q4" t="n">
         <v>1.76430389369373</v>
       </c>
-      <c r="N4" t="n">
+      <c r="R4" t="n">
         <v>2.172864444444444</v>
       </c>
-      <c r="O4" t="n">
+      <c r="S4" t="n">
         <v>1.175532510248361</v>
       </c>
-      <c r="P4" t="n">
+      <c r="T4" t="n">
+        <v>1.382598192059179</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.503649597066818</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="V4" t="n">
         <v>0.8008488888888888</v>
       </c>
     </row>
@@ -1021,45 +1171,60 @@
         <v>0.648825474506432</v>
       </c>
       <c r="D5" t="n">
+        <v>0.4603870171584926</v>
+      </c>
+      <c r="E5" t="n">
         <v>0.3324894975031868</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
       <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
         <v>0.05332792378797025</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
+        <v>0.229514062249939</v>
+      </c>
+      <c r="I5" t="n">
         <v>0.2398019925813007</v>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>0.01287</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>18.15397590457117</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
+        <v>10.56197887296547</v>
+      </c>
+      <c r="M5" t="n">
         <v>21.60541685701685</v>
       </c>
-      <c r="K5" t="n">
+      <c r="N5" t="n">
         <v>12.44194428571429</v>
       </c>
-      <c r="L5" t="n">
+      <c r="O5" t="n">
         <v>1.511592918818219</v>
       </c>
-      <c r="M5" t="n">
+      <c r="P5" t="n">
+        <v>3.04720056954267</v>
+      </c>
+      <c r="Q5" t="n">
         <v>2.180907715972913</v>
       </c>
-      <c r="N5" t="n">
+      <c r="R5" t="n">
         <v>2.03551</v>
       </c>
-      <c r="O5" t="n">
+      <c r="S5" t="n">
         <v>0.7377259504025687</v>
       </c>
-      <c r="P5" t="n">
+      <c r="T5" t="n">
+        <v>1.247851006655203</v>
+      </c>
+      <c r="U5" t="n">
         <v>1.073121809444153</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="V5" t="n">
         <v>0.5652685714285715</v>
       </c>
     </row>
@@ -1076,45 +1241,60 @@
         <v>0.7073266501059357</v>
       </c>
       <c r="D6" t="n">
+        <v>0.008306149571100641</v>
+      </c>
+      <c r="E6" t="n">
         <v>0.4853916265043956</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>0.0118075</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>0.1195185320505014</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
+        <v>0.7426201039867404</v>
+      </c>
+      <c r="I6" t="n">
         <v>0.317470690161681</v>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>0.20985</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>8.345925088891294</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
+        <v>16.91911264320431</v>
+      </c>
+      <c r="M6" t="n">
         <v>14.11109001702911</v>
       </c>
-      <c r="K6" t="n">
+      <c r="N6" t="n">
         <v>124.3020025</v>
       </c>
-      <c r="L6" t="n">
+      <c r="O6" t="n">
         <v>1.397779422538644</v>
       </c>
-      <c r="M6" t="n">
+      <c r="P6" t="n">
+        <v>2.277652313042076</v>
+      </c>
+      <c r="Q6" t="n">
         <v>1.991039052373869</v>
       </c>
-      <c r="N6" t="n">
+      <c r="R6" t="n">
         <v>1.4812675</v>
       </c>
-      <c r="O6" t="n">
+      <c r="S6" t="n">
         <v>1.044008037374732</v>
       </c>
-      <c r="P6" t="n">
+      <c r="T6" t="n">
+        <v>1.530175571948459</v>
+      </c>
+      <c r="U6" t="n">
         <v>1.527836775714004</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="V6" t="n">
         <v>0.9322775</v>
       </c>
     </row>
@@ -1131,45 +1311,60 @@
         <v>0.646785681189351</v>
       </c>
       <c r="D7" t="n">
+        <v>0.0274395329441201</v>
+      </c>
+      <c r="E7" t="n">
         <v>0.3925268411506944</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>0.002313333333333333</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>0.1909722222222222</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="I7" t="n">
         <v>0.3406339031339032</v>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>0.01852</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>15.75042301538382</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
+        <v>33.72926960168589</v>
+      </c>
+      <c r="M7" t="n">
         <v>20.81801974629931</v>
       </c>
-      <c r="K7" t="n">
+      <c r="N7" t="n">
         <v>15.22302</v>
       </c>
-      <c r="L7" t="n">
+      <c r="O7" t="n">
         <v>1.363439205771523</v>
       </c>
-      <c r="M7" t="n">
+      <c r="P7" t="n">
+        <v>2.124647410035351</v>
+      </c>
+      <c r="Q7" t="n">
         <v>1.729715533719212</v>
       </c>
-      <c r="N7" t="n">
+      <c r="R7" t="n">
         <v>1.40933</v>
       </c>
-      <c r="O7" t="n">
+      <c r="S7" t="n">
         <v>0.6486265192006623</v>
       </c>
-      <c r="P7" t="n">
+      <c r="T7" t="n">
+        <v>1.516066561280623</v>
+      </c>
+      <c r="U7" t="n">
         <v>0.8554778262487797</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="V7" t="n">
         <v>1.510403333333334</v>
       </c>
     </row>
@@ -1186,45 +1381,60 @@
         <v>0.6602145501583478</v>
       </c>
       <c r="D8" t="n">
+        <v>0.08939393939393939</v>
+      </c>
+      <c r="E8" t="n">
         <v>0.2850464703234675</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>0.00238</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>0.1029499850254567</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
+        <v>0.5063941299790357</v>
+      </c>
+      <c r="I8" t="n">
         <v>0.4526305281022261</v>
       </c>
-      <c r="H8" t="n">
+      <c r="J8" t="n">
         <v>0.0452375</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>11.19120996675137</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
+        <v>66.86684543998506</v>
+      </c>
+      <c r="M8" t="n">
         <v>29.43392136563681</v>
       </c>
-      <c r="K8" t="n">
+      <c r="N8" t="n">
         <v>14.7363825</v>
       </c>
-      <c r="L8" t="n">
+      <c r="O8" t="n">
         <v>1.170859612129497</v>
       </c>
-      <c r="M8" t="n">
+      <c r="P8" t="n">
+        <v>2.320877531752856</v>
+      </c>
+      <c r="Q8" t="n">
         <v>1.638376067706995</v>
       </c>
-      <c r="N8" t="n">
+      <c r="R8" t="n">
         <v>1.548865</v>
       </c>
-      <c r="O8" t="n">
+      <c r="S8" t="n">
         <v>0.6029241681024269</v>
       </c>
-      <c r="P8" t="n">
+      <c r="T8" t="n">
+        <v>1.143461385956914</v>
+      </c>
+      <c r="U8" t="n">
         <v>1.021211652919317</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="V8" t="n">
         <v>1.2671325</v>
       </c>
     </row>
@@ -1241,45 +1451,60 @@
         <v>0.8947830662351912</v>
       </c>
       <c r="D9" t="n">
+        <v>0.07789092758748802</v>
+      </c>
+      <c r="E9" t="n">
         <v>0.285213393649189</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
       <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
         <v>0.03617723396366333</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
+        <v>0.4482295142751205</v>
+      </c>
+      <c r="I9" t="n">
         <v>0.4724286243974787</v>
       </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>7.412136935120854</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
+        <v>29.81740891745856</v>
+      </c>
+      <c r="M9" t="n">
         <v>18.45932391726101</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
         <v>1.080502155345708</v>
       </c>
-      <c r="M9" t="n">
+      <c r="P9" t="n">
+        <v>1.849792943651527</v>
+      </c>
+      <c r="Q9" t="n">
         <v>1.447897086241719</v>
       </c>
-      <c r="N9" t="n">
+      <c r="R9" t="n">
         <v>1.2152875</v>
       </c>
-      <c r="O9" t="n">
+      <c r="S9" t="n">
         <v>0.9183410949428793</v>
       </c>
-      <c r="P9" t="n">
+      <c r="T9" t="n">
+        <v>1.156565299136231</v>
+      </c>
+      <c r="U9" t="n">
         <v>1.137856880613049</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="V9" t="n">
         <v>1.2085275</v>
       </c>
     </row>
@@ -1296,45 +1521,60 @@
         <v>0.8342493627621366</v>
       </c>
       <c r="D10" t="n">
+        <v>0.04513888888888889</v>
+      </c>
+      <c r="E10" t="n">
         <v>0.4498530666413878</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
       <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
         <v>0.06083864246503987</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
+        <v>0.8134571462916216</v>
+      </c>
+      <c r="I10" t="n">
         <v>0.4269313218736226</v>
       </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>18.17708920627782</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
+        <v>45.91494433861459</v>
+      </c>
+      <c r="M10" t="n">
         <v>24.34280196846024</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
         <v>1.058539902277871</v>
       </c>
-      <c r="M10" t="n">
+      <c r="P10" t="n">
+        <v>1.561495532782094</v>
+      </c>
+      <c r="Q10" t="n">
         <v>1.337862903330572</v>
       </c>
-      <c r="N10" t="n">
+      <c r="R10" t="n">
         <v>1.068886666666667</v>
       </c>
-      <c r="O10" t="n">
+      <c r="S10" t="n">
         <v>0.5196140591547947</v>
       </c>
-      <c r="P10" t="n">
+      <c r="T10" t="n">
+        <v>1.164799402468186</v>
+      </c>
+      <c r="U10" t="n">
         <v>1.190633507835879</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="V10" t="n">
         <v>1.38858</v>
       </c>
     </row>
@@ -1351,45 +1591,60 @@
         <v>0.7634610518759121</v>
       </c>
       <c r="D11" t="n">
+        <v>0.2586462305229958</v>
+      </c>
+      <c r="E11" t="n">
         <v>0.2128686508496917</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>0.0039675</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>0.07394071957114863</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
+        <v>0.2643339133805958</v>
+      </c>
+      <c r="I11" t="n">
         <v>0.5591602025332514</v>
       </c>
-      <c r="H11" t="n">
+      <c r="J11" t="n">
         <v>0.0059525</v>
       </c>
-      <c r="I11" t="n">
+      <c r="K11" t="n">
         <v>7.163652543576848</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
+        <v>10.66381825705897</v>
+      </c>
+      <c r="M11" t="n">
         <v>24.6929802122293</v>
       </c>
-      <c r="K11" t="n">
+      <c r="N11" t="n">
         <v>1.88055</v>
       </c>
-      <c r="L11" t="n">
+      <c r="O11" t="n">
         <v>1.278212304963092</v>
       </c>
-      <c r="M11" t="n">
+      <c r="P11" t="n">
+        <v>4.276509061527879</v>
+      </c>
+      <c r="Q11" t="n">
         <v>1.81614614512335</v>
       </c>
-      <c r="N11" t="n">
+      <c r="R11" t="n">
         <v>2.865035</v>
       </c>
-      <c r="O11" t="n">
+      <c r="S11" t="n">
         <v>0.8864181812884088</v>
       </c>
-      <c r="P11" t="n">
+      <c r="T11" t="n">
+        <v>1.787721201624736</v>
+      </c>
+      <c r="U11" t="n">
         <v>1.109651112763468</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="V11" t="n">
         <v>1.4339175</v>
       </c>
     </row>
@@ -1406,45 +1661,60 @@
         <v>0.8937054758865601</v>
       </c>
       <c r="D12" t="n">
+        <v>0.1800158783358173</v>
+      </c>
+      <c r="E12" t="n">
         <v>0.3327159085236713</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>0.007126666666666667</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>0.03346355505294541</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
+        <v>0.3665487040183257</v>
+      </c>
+      <c r="I12" t="n">
         <v>0.4203312280939759</v>
       </c>
-      <c r="H12" t="n">
+      <c r="J12" t="n">
         <v>0.02590666666666666</v>
       </c>
-      <c r="I12" t="n">
+      <c r="K12" t="n">
         <v>6.399779753725301</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
+        <v>17.17114366892259</v>
+      </c>
+      <c r="M12" t="n">
         <v>20.2656918310027</v>
       </c>
-      <c r="K12" t="n">
+      <c r="N12" t="n">
         <v>23.01191333333334</v>
       </c>
-      <c r="L12" t="n">
+      <c r="O12" t="n">
         <v>1.3144131578935</v>
       </c>
-      <c r="M12" t="n">
+      <c r="P12" t="n">
+        <v>3.588246465843827</v>
+      </c>
+      <c r="Q12" t="n">
         <v>1.887839859784966</v>
       </c>
-      <c r="N12" t="n">
+      <c r="R12" t="n">
         <v>2.356353333333333</v>
       </c>
-      <c r="O12" t="n">
+      <c r="S12" t="n">
         <v>0.6465418437324721</v>
       </c>
-      <c r="P12" t="n">
+      <c r="T12" t="n">
+        <v>1.357885358246975</v>
+      </c>
+      <c r="U12" t="n">
         <v>0.9309593129122237</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="V12" t="n">
         <v>0.63754</v>
       </c>
     </row>
@@ -1459,7 +1729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q51"/>
+  <dimension ref="A1:V51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1480,70 +1750,95 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Phys. contact@5mm·OmniRetarget</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Phys. contact@5mm·SBTO</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Phys. contact@5mm·GMR</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Phys. penetration@5mm·SPIDER-CEM</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Phys. penetration@5mm·OmniRetarget</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Phys. penetration@5mm·SBTO</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Phys. penetration@5mm·GMR</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Max phys penetration (mm)·SPIDER-CEM</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Max phys penetration (mm)·OmniRetarget</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Max phys penetration (mm)·SBTO</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Max phys penetration (mm)·GMR</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Obj speed max (m/s)·SPIDER-CEM</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Obj speed max (m/s)·OmniRetarget</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Obj speed max (m/s)·SBTO</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Obj speed max (m/s)·GMR</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Foot slip max (m)·SPIDER-CEM</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Foot slip max (m)·OmniRetarget</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Foot slip max (m)·SBTO</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Foot slip max (m)·GMR</t>
         </is>
@@ -1564,45 +1859,60 @@
         <v>0.5616438356164384</v>
       </c>
       <c r="D2" t="n">
+        <v>0.0547945205479452</v>
+      </c>
+      <c r="E2" t="n">
         <v>0.2191780821917808</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
       <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
         <v>0.171875</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
+        <v>0.5390625</v>
+      </c>
+      <c r="I2" t="n">
         <v>0.3515625</v>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
         <v>11.22467534272482</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
+        <v>14.75487797391276</v>
+      </c>
+      <c r="M2" t="n">
         <v>38.716000842528</v>
       </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
         <v>1.720945334417766</v>
       </c>
-      <c r="M2" t="n">
+      <c r="P2" t="n">
+        <v>1.825377090524115</v>
+      </c>
+      <c r="Q2" t="n">
         <v>1.993880877005211</v>
       </c>
-      <c r="N2" t="n">
+      <c r="R2" t="n">
         <v>1.16776</v>
       </c>
-      <c r="O2" t="n">
+      <c r="S2" t="n">
         <v>0.4989995143715082</v>
       </c>
-      <c r="P2" t="n">
+      <c r="T2" t="n">
+        <v>1.940457544622395</v>
+      </c>
+      <c r="U2" t="n">
         <v>1.920229269667622</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="V2" t="n">
         <v>0.22416</v>
       </c>
     </row>
@@ -1621,45 +1931,60 @@
         <v>0.9206349206349206</v>
       </c>
       <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.492063492063492</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
       <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
         <v>0.04</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="I3" t="n">
         <v>0.2</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
         <v>12.41579905025665</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
+        <v>16.00160503866953</v>
+      </c>
+      <c r="M3" t="n">
         <v>12.56974851097305</v>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
         <v>0.8414709189358631</v>
       </c>
-      <c r="M3" t="n">
+      <c r="P3" t="n">
+        <v>2.644874467534997</v>
+      </c>
+      <c r="Q3" t="n">
         <v>1.164705155213796</v>
       </c>
-      <c r="N3" t="n">
+      <c r="R3" t="n">
         <v>1.8105</v>
       </c>
-      <c r="O3" t="n">
+      <c r="S3" t="n">
         <v>0.5987264463276435</v>
       </c>
-      <c r="P3" t="n">
+      <c r="T3" t="n">
+        <v>0.6599132234079145</v>
+      </c>
+      <c r="U3" t="n">
         <v>0.6371548279627192</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="V3" t="n">
         <v>0.63137</v>
       </c>
     </row>
@@ -1678,45 +2003,60 @@
         <v>0.7874015748031497</v>
       </c>
       <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.4881889763779528</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
       <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
         <v>0.07006369426751592</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
+        <v>0.8471337579617835</v>
+      </c>
+      <c r="I4" t="n">
         <v>0.1464968152866242</v>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>13.29757291934628</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
+        <v>17.09141372113309</v>
+      </c>
+      <c r="M4" t="n">
         <v>13.77360827363477</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
         <v>0.799177623266594</v>
       </c>
-      <c r="M4" t="n">
+      <c r="P4" t="n">
+        <v>2.231432482933561</v>
+      </c>
+      <c r="Q4" t="n">
         <v>1.181751696337448</v>
       </c>
-      <c r="N4" t="n">
+      <c r="R4" t="n">
         <v>1.52748</v>
       </c>
-      <c r="O4" t="n">
+      <c r="S4" t="n">
         <v>1.494186403639363</v>
       </c>
-      <c r="P4" t="n">
+      <c r="T4" t="n">
+        <v>1.524256642876222</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.362291845095622</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="V4" t="n">
         <v>0.80903</v>
       </c>
     </row>
@@ -1735,45 +2075,60 @@
         <v>0.8157894736842105</v>
       </c>
       <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
         <v>0.631578947368421</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
       <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
         <v>0.03478260869565217</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
+        <v>0.6695652173913044</v>
+      </c>
+      <c r="I5" t="n">
         <v>0.0782608695652174</v>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>0.05128</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>7.564805310868932</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
+        <v>18.40694922670669</v>
+      </c>
+      <c r="M5" t="n">
         <v>10.86817275315835</v>
       </c>
-      <c r="K5" t="n">
+      <c r="N5" t="n">
         <v>44.92938</v>
       </c>
-      <c r="L5" t="n">
+      <c r="O5" t="n">
         <v>1.409627392421537</v>
       </c>
-      <c r="M5" t="n">
+      <c r="P5" t="n">
+        <v>2.13651685497919</v>
+      </c>
+      <c r="Q5" t="n">
         <v>1.730230592399101</v>
       </c>
-      <c r="N5" t="n">
+      <c r="R5" t="n">
         <v>1.36184</v>
       </c>
-      <c r="O5" t="n">
+      <c r="S5" t="n">
         <v>0.2719325849563114</v>
       </c>
-      <c r="P5" t="n">
+      <c r="T5" t="n">
+        <v>0.9913845032750463</v>
+      </c>
+      <c r="U5" t="n">
         <v>1.131543879688549</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="V5" t="n">
         <v>1.03852</v>
       </c>
     </row>
@@ -1792,45 +2147,60 @@
         <v>0.8095238095238095</v>
       </c>
       <c r="D6" t="n">
+        <v>0.03571428571428571</v>
+      </c>
+      <c r="E6" t="n">
         <v>0.3809523809523809</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
       <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>0.03361344537815126</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
+        <v>0.6638655462184874</v>
+      </c>
+      <c r="I6" t="n">
         <v>0.4033613445378151</v>
       </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
         <v>5.389112385506452</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
+        <v>18.47157660412482</v>
+      </c>
+      <c r="M6" t="n">
         <v>11.19391350488835</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
         <v>0.9076237451906026</v>
       </c>
-      <c r="M6" t="n">
+      <c r="P6" t="n">
+        <v>1.419164310303154</v>
+      </c>
+      <c r="Q6" t="n">
         <v>1.384293200853355</v>
       </c>
-      <c r="N6" t="n">
+      <c r="R6" t="n">
         <v>0.9432</v>
       </c>
-      <c r="O6" t="n">
+      <c r="S6" t="n">
         <v>0.910981566957671</v>
       </c>
-      <c r="P6" t="n">
+      <c r="T6" t="n">
+        <v>1.053914778919496</v>
+      </c>
+      <c r="U6" t="n">
         <v>0.9955719109480666</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="V6" t="n">
         <v>1.15033</v>
       </c>
     </row>
@@ -1849,45 +2219,60 @@
         <v>0.5975609756097561</v>
       </c>
       <c r="D7" t="n">
+        <v>0.01219512195121951</v>
+      </c>
+      <c r="E7" t="n">
         <v>0.08536585365853659</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.2336448598130841</v>
+      </c>
+      <c r="I7" t="n">
         <v>0.1682242990654206</v>
       </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>4.790446269104168</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
+        <v>18.45745347140345</v>
+      </c>
+      <c r="M7" t="n">
         <v>11.89498481993016</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
         <v>1.150657246960274</v>
       </c>
-      <c r="M7" t="n">
+      <c r="P7" t="n">
+        <v>1.425279042698989</v>
+      </c>
+      <c r="Q7" t="n">
         <v>1.455258638659611</v>
       </c>
-      <c r="N7" t="n">
+      <c r="R7" t="n">
         <v>0.9432</v>
       </c>
-      <c r="O7" t="n">
+      <c r="S7" t="n">
         <v>1.218834115723769</v>
       </c>
-      <c r="P7" t="n">
+      <c r="T7" t="n">
+        <v>1.194914756764223</v>
+      </c>
+      <c r="U7" t="n">
         <v>1.21423355133621</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="V7" t="n">
         <v>1.21928</v>
       </c>
     </row>
@@ -1906,45 +2291,60 @@
         <v>0.8103448275862069</v>
       </c>
       <c r="D8" t="n">
+        <v>0.6379310344827587</v>
+      </c>
+      <c r="E8" t="n">
         <v>0.3793103448275862</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
       <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
         <v>0.04195804195804196</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
+        <v>0.2937062937062937</v>
+      </c>
+      <c r="I8" t="n">
         <v>0.5034965034965035</v>
       </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>6.617578762436553</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
+        <v>8.786737891551578</v>
+      </c>
+      <c r="M8" t="n">
         <v>72.21469964075384</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
         <v>1.442718529569813</v>
       </c>
-      <c r="M8" t="n">
+      <c r="P8" t="n">
+        <v>4.207446236125632</v>
+      </c>
+      <c r="Q8" t="n">
         <v>1.626696140327053</v>
       </c>
-      <c r="N8" t="n">
+      <c r="R8" t="n">
         <v>2.77386</v>
       </c>
-      <c r="O8" t="n">
+      <c r="S8" t="n">
         <v>2.33441959332199</v>
       </c>
-      <c r="P8" t="n">
+      <c r="T8" t="n">
+        <v>2.404735224195784</v>
+      </c>
+      <c r="U8" t="n">
         <v>2.376978856501543</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="V8" t="n">
         <v>1.34281</v>
       </c>
     </row>
@@ -1963,45 +2363,60 @@
         <v>0.864</v>
       </c>
       <c r="D9" t="n">
+        <v>0.888</v>
+      </c>
+      <c r="E9" t="n">
         <v>0.288</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
       <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
         <v>0.08053691275167785</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
+        <v>0.09395973154362416</v>
+      </c>
+      <c r="I9" t="n">
         <v>0.4832214765100671</v>
       </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>24.33864790607865</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
+        <v>8.190288664048911</v>
+      </c>
+      <c r="M9" t="n">
         <v>30.31949432827938</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
         <v>1.586919916136492</v>
       </c>
-      <c r="M9" t="n">
+      <c r="P9" t="n">
+        <v>4.275868665871768</v>
+      </c>
+      <c r="Q9" t="n">
         <v>2.260766006720658</v>
       </c>
-      <c r="N9" t="n">
+      <c r="R9" t="n">
         <v>2.77386</v>
       </c>
-      <c r="O9" t="n">
+      <c r="S9" t="n">
         <v>1.583066285164315</v>
       </c>
-      <c r="P9" t="n">
+      <c r="T9" t="n">
+        <v>2.361298804373485</v>
+      </c>
+      <c r="U9" t="n">
         <v>2.305046630799262</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="V9" t="n">
         <v>1.05022</v>
       </c>
     </row>
@@ -2020,45 +2435,60 @@
         <v>0.7213114754098361</v>
       </c>
       <c r="D10" t="n">
+        <v>0.3114754098360656</v>
+      </c>
+      <c r="E10" t="n">
         <v>0.4672131147540984</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>0.00709</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>0.08391608391608392</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
+        <v>0.6083916083916084</v>
+      </c>
+      <c r="I10" t="n">
         <v>0.3356643356643357</v>
       </c>
-      <c r="H10" t="n">
+      <c r="J10" t="n">
         <v>0.39007</v>
       </c>
-      <c r="I10" t="n">
+      <c r="K10" t="n">
         <v>11.07068899199398</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
+        <v>8.653045113286352</v>
+      </c>
+      <c r="M10" t="n">
         <v>25.46006251754338</v>
       </c>
-      <c r="K10" t="n">
+      <c r="N10" t="n">
         <v>190.59953</v>
       </c>
-      <c r="L10" t="n">
+      <c r="O10" t="n">
         <v>1.220922873504122</v>
       </c>
-      <c r="M10" t="n">
+      <c r="P10" t="n">
+        <v>2.77569584911045</v>
+      </c>
+      <c r="Q10" t="n">
         <v>1.588893540005631</v>
       </c>
-      <c r="N10" t="n">
+      <c r="R10" t="n">
         <v>1.82995</v>
       </c>
-      <c r="O10" t="n">
+      <c r="S10" t="n">
         <v>1.663572408805639</v>
       </c>
-      <c r="P10" t="n">
+      <c r="T10" t="n">
+        <v>1.603472249968406</v>
+      </c>
+      <c r="U10" t="n">
         <v>1.734007470318301</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="V10" t="n">
         <v>0.40976</v>
       </c>
     </row>
@@ -2077,45 +2507,60 @@
         <v>0.4411764705882353</v>
       </c>
       <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
         <v>0.4509803921568628</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
       <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
         <v>0.08870967741935484</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
+        <v>0.008064516129032258</v>
+      </c>
+      <c r="I11" t="n">
         <v>0.4354838709677419</v>
       </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>13.38241913620393</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
+        <v>8.944048412265222</v>
+      </c>
+      <c r="M11" t="n">
         <v>41.00086099343271</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
         <v>1.099978799302246</v>
       </c>
-      <c r="M11" t="n">
+      <c r="P11" t="n">
+        <v>3.368856776366021</v>
+      </c>
+      <c r="Q11" t="n">
         <v>1.653577398856196</v>
       </c>
-      <c r="N11" t="n">
+      <c r="R11" t="n">
         <v>2.18546</v>
       </c>
-      <c r="O11" t="n">
+      <c r="S11" t="n">
         <v>1.783966649322894</v>
       </c>
-      <c r="P11" t="n">
+      <c r="T11" t="n">
+        <v>1.639091117855975</v>
+      </c>
+      <c r="U11" t="n">
         <v>1.708690175750377</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="V11" t="n">
         <v>1.61516</v>
       </c>
     </row>
@@ -2134,45 +2579,60 @@
         <v>0.8604651162790697</v>
       </c>
       <c r="D12" t="n">
+        <v>0.2209302325581395</v>
+      </c>
+      <c r="E12" t="n">
         <v>0.2674418604651163</v>
       </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.5964912280701754</v>
+      </c>
+      <c r="I12" t="n">
         <v>0.4035087719298245</v>
       </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>4.515228133653084</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
+        <v>9.973732330659507</v>
+      </c>
+      <c r="M12" t="n">
         <v>16.16226908043172</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
         <v>1.074921048091458</v>
       </c>
-      <c r="M12" t="n">
+      <c r="P12" t="n">
+        <v>1.429072735241391</v>
+      </c>
+      <c r="Q12" t="n">
         <v>1.550775841808834</v>
       </c>
-      <c r="N12" t="n">
+      <c r="R12" t="n">
         <v>0.94215</v>
       </c>
-      <c r="O12" t="n">
+      <c r="S12" t="n">
         <v>0.5680474277227558</v>
       </c>
-      <c r="P12" t="n">
+      <c r="T12" t="n">
+        <v>1.01296355346179</v>
+      </c>
+      <c r="U12" t="n">
         <v>1.531093456030802</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="V12" t="n">
         <v>0.32796</v>
       </c>
     </row>
@@ -2191,45 +2651,60 @@
         <v>0.4264705882352941</v>
       </c>
       <c r="D13" t="n">
+        <v>0.7205882352941176</v>
+      </c>
+      <c r="E13" t="n">
         <v>0.1617647058823529</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
       <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
         <v>0.1627906976744186</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
+        <v>0.2325581395348837</v>
+      </c>
+      <c r="I13" t="n">
         <v>0.5465116279069767</v>
       </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
         <v>10.91603121892292</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
+        <v>7.055045879805565</v>
+      </c>
+      <c r="M13" t="n">
         <v>72.04498595265696</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
         <v>1.265138069404463</v>
       </c>
-      <c r="M13" t="n">
+      <c r="P13" t="n">
+        <v>4.078999997899763</v>
+      </c>
+      <c r="Q13" t="n">
         <v>2.038601440903175</v>
       </c>
-      <c r="N13" t="n">
+      <c r="R13" t="n">
         <v>2.60001</v>
       </c>
-      <c r="O13" t="n">
+      <c r="S13" t="n">
         <v>0.4191837792850998</v>
       </c>
-      <c r="P13" t="n">
+      <c r="T13" t="n">
+        <v>0.6892000158079087</v>
+      </c>
+      <c r="U13" t="n">
         <v>0.4555608936126307</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="V13" t="n">
         <v>0.07931000000000001</v>
       </c>
     </row>
@@ -2248,45 +2723,60 @@
         <v>0.5230769230769231</v>
       </c>
       <c r="D14" t="n">
+        <v>0.4307692307692308</v>
+      </c>
+      <c r="E14" t="n">
         <v>0.3692307692307693</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
       <c r="F14" t="n">
-        <v>0.09615384615384616</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
         <v>0.09615384615384616</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>0.3365384615384616</v>
       </c>
       <c r="I14" t="n">
+        <v>0.09615384615384616</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
         <v>19.10200759437637</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
+        <v>8.745306051929692</v>
+      </c>
+      <c r="M14" t="n">
         <v>23.08105005021237</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
         <v>1.480694327186641</v>
       </c>
-      <c r="M14" t="n">
+      <c r="P14" t="n">
+        <v>4.350156367207457</v>
+      </c>
+      <c r="Q14" t="n">
         <v>1.937977912907278</v>
       </c>
-      <c r="N14" t="n">
+      <c r="R14" t="n">
         <v>2.77285</v>
       </c>
-      <c r="O14" t="n">
+      <c r="S14" t="n">
         <v>0.2263884685656425</v>
       </c>
-      <c r="P14" t="n">
+      <c r="T14" t="n">
+        <v>0.3042510850095115</v>
+      </c>
+      <c r="U14" t="n">
         <v>1.148846193451786</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="V14" t="n">
         <v>0.05813</v>
       </c>
     </row>
@@ -2305,45 +2795,60 @@
         <v>0.6730769230769231</v>
       </c>
       <c r="D15" t="n">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="E15" t="n">
         <v>0.4423076923076923</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
       <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
         <v>0.07476635514018691</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
+        <v>0.1214953271028037</v>
+      </c>
+      <c r="I15" t="n">
         <v>0.1308411214953271</v>
       </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>10.73230293433133</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
+        <v>6.03688961166813</v>
+      </c>
+      <c r="M15" t="n">
         <v>49.68875696507697</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
         <v>1.567702412793432</v>
       </c>
-      <c r="M15" t="n">
+      <c r="P15" t="n">
+        <v>2.898727765045833</v>
+      </c>
+      <c r="Q15" t="n">
         <v>1.71468780309401</v>
       </c>
-      <c r="N15" t="n">
+      <c r="R15" t="n">
         <v>1.84769</v>
       </c>
-      <c r="O15" t="n">
+      <c r="S15" t="n">
         <v>0.6102408977541703</v>
       </c>
-      <c r="P15" t="n">
+      <c r="T15" t="n">
+        <v>0.7333267933120833</v>
+      </c>
+      <c r="U15" t="n">
         <v>0.6462637610483477</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="V15" t="n">
         <v>0.74287</v>
       </c>
     </row>
@@ -2362,45 +2867,60 @@
         <v>0.7815126050420168</v>
       </c>
       <c r="D16" t="n">
+        <v>0.6722689075630253</v>
+      </c>
+      <c r="E16" t="n">
         <v>0.2941176470588235</v>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
       <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
         <v>0.1319444444444444</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
+        <v>0.2708333333333333</v>
+      </c>
+      <c r="I16" t="n">
         <v>0.4861111111111111</v>
       </c>
-      <c r="H16" t="n">
+      <c r="J16" t="n">
         <v>0.6137899999999999</v>
       </c>
-      <c r="I16" t="n">
+      <c r="K16" t="n">
         <v>39.20417460037603</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
+        <v>9.840408816627251</v>
+      </c>
+      <c r="M16" t="n">
         <v>30.45770465819981</v>
       </c>
-      <c r="K16" t="n">
+      <c r="N16" t="n">
         <v>174.64764</v>
       </c>
-      <c r="L16" t="n">
+      <c r="O16" t="n">
         <v>1.223215437775004</v>
       </c>
-      <c r="M16" t="n">
+      <c r="P16" t="n">
+        <v>2.820834806017193</v>
+      </c>
+      <c r="Q16" t="n">
         <v>1.506758958620737</v>
       </c>
-      <c r="N16" t="n">
+      <c r="R16" t="n">
         <v>1.82995</v>
       </c>
-      <c r="O16" t="n">
+      <c r="S16" t="n">
         <v>1.390907082292746</v>
       </c>
-      <c r="P16" t="n">
+      <c r="T16" t="n">
+        <v>1.695044884547667</v>
+      </c>
+      <c r="U16" t="n">
         <v>1.626358936088308</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="V16" t="n">
         <v>1.58142</v>
       </c>
     </row>
@@ -2419,45 +2939,60 @@
         <v>0.7301587301587301</v>
       </c>
       <c r="D17" t="n">
+        <v>0.126984126984127</v>
+      </c>
+      <c r="E17" t="n">
         <v>0.1587301587301587</v>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
       <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
         <v>0.009803921568627451</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
+        <v>0.5490196078431373</v>
+      </c>
+      <c r="I17" t="n">
         <v>0.4215686274509804</v>
       </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
         <v>5.503541580577019</v>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
+        <v>10.74407918270679</v>
+      </c>
+      <c r="M17" t="n">
         <v>67.400052907233</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
         <v>1.12907047000013</v>
       </c>
-      <c r="M17" t="n">
+      <c r="P17" t="n">
+        <v>2.40270561217862</v>
+      </c>
+      <c r="Q17" t="n">
         <v>1.585315376411575</v>
       </c>
-      <c r="N17" t="n">
+      <c r="R17" t="n">
         <v>1.64472</v>
       </c>
-      <c r="O17" t="n">
+      <c r="S17" t="n">
         <v>0.9608202053366027</v>
       </c>
-      <c r="P17" t="n">
+      <c r="T17" t="n">
+        <v>1.033202832353973</v>
+      </c>
+      <c r="U17" t="n">
         <v>1.225652786160491</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="V17" t="n">
         <v>1.076</v>
       </c>
     </row>
@@ -2476,45 +3011,60 @@
         <v>0.5833333333333334</v>
       </c>
       <c r="D18" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="E18" t="n">
         <v>0.3055555555555556</v>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
       <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
         <v>0.06666666666666667</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
+        <v>0.6190476190476191</v>
+      </c>
+      <c r="I18" t="n">
         <v>0.3428571428571429</v>
       </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
         <v>10.11631492827088</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
+        <v>15.18009117823281</v>
+      </c>
+      <c r="M18" t="n">
         <v>18.57246326291231</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
         <v>1.157220862080101</v>
       </c>
-      <c r="M18" t="n">
+      <c r="P18" t="n">
+        <v>2.417986045241287</v>
+      </c>
+      <c r="Q18" t="n">
         <v>1.694308478342395</v>
       </c>
-      <c r="N18" t="n">
+      <c r="R18" t="n">
         <v>1.64472</v>
       </c>
-      <c r="O18" t="n">
+      <c r="S18" t="n">
         <v>0.7114226505068965</v>
       </c>
-      <c r="P18" t="n">
+      <c r="T18" t="n">
+        <v>1.007175352246982</v>
+      </c>
+      <c r="U18" t="n">
         <v>0.6484833812592544</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="V18" t="n">
         <v>0.54445</v>
       </c>
     </row>
@@ -2533,45 +3083,60 @@
         <v>0.5573770491803278</v>
       </c>
       <c r="D19" t="n">
+        <v>0.2459016393442623</v>
+      </c>
+      <c r="E19" t="n">
         <v>0.3770491803278688</v>
       </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
       <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
         <v>0.04587155963302753</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
+        <v>0.3761467889908257</v>
+      </c>
+      <c r="I19" t="n">
         <v>0.3119266055045872</v>
       </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>6.054606640987176</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
+        <v>13.73016608490209</v>
+      </c>
+      <c r="M19" t="n">
         <v>28.11284391613936</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
         <v>1.803880025648794</v>
       </c>
-      <c r="M19" t="n">
+      <c r="P19" t="n">
+        <v>5.697912136969935</v>
+      </c>
+      <c r="Q19" t="n">
         <v>2.384342801847548</v>
       </c>
-      <c r="N19" t="n">
+      <c r="R19" t="n">
         <v>3.90039</v>
       </c>
-      <c r="O19" t="n">
+      <c r="S19" t="n">
         <v>1.632040107686994</v>
       </c>
-      <c r="P19" t="n">
+      <c r="T19" t="n">
+        <v>1.345057277145403</v>
+      </c>
+      <c r="U19" t="n">
         <v>1.685224397808024</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="V19" t="n">
         <v>0.70029</v>
       </c>
     </row>
@@ -2590,45 +3155,60 @@
         <v>0.5</v>
       </c>
       <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
         <v>0.4456521739130435</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>0.02439</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>0.3109243697478992</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
+        <v>0.8067226890756303</v>
+      </c>
+      <c r="I20" t="n">
         <v>0.3865546218487395</v>
       </c>
-      <c r="H20" t="n">
+      <c r="J20" t="n">
         <v>0.01626</v>
       </c>
-      <c r="I20" t="n">
+      <c r="K20" t="n">
         <v>10.04062827063681</v>
       </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
+        <v>15.86103472907423</v>
+      </c>
+      <c r="M20" t="n">
         <v>17.29351325628774</v>
       </c>
-      <c r="K20" t="n">
+      <c r="N20" t="n">
         <v>21.99605</v>
       </c>
-      <c r="L20" t="n">
+      <c r="O20" t="n">
         <v>1.261037375057706</v>
       </c>
-      <c r="M20" t="n">
+      <c r="P20" t="n">
+        <v>1.401126365396893</v>
+      </c>
+      <c r="Q20" t="n">
         <v>1.597980050826762</v>
       </c>
-      <c r="N20" t="n">
+      <c r="R20" t="n">
         <v>0.9237300000000001</v>
       </c>
-      <c r="O20" t="n">
+      <c r="S20" t="n">
         <v>1.016111333933175</v>
       </c>
-      <c r="P20" t="n">
+      <c r="T20" t="n">
+        <v>1.806961225475799</v>
+      </c>
+      <c r="U20" t="n">
         <v>1.708690022335908</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="V20" t="n">
         <v>1.22797</v>
       </c>
     </row>
@@ -2647,45 +3227,60 @@
         <v>0.7752808988764045</v>
       </c>
       <c r="D21" t="n">
+        <v>0.02247191011235955</v>
+      </c>
+      <c r="E21" t="n">
         <v>0.5056179775280899</v>
       </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
       <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
         <v>0.0782608695652174</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
+        <v>0.7739130434782608</v>
+      </c>
+      <c r="I21" t="n">
         <v>0.3217391304347826</v>
       </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
         <v>8.038073923660505</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
+        <v>16.24224694487645</v>
+      </c>
+      <c r="M21" t="n">
         <v>14.04678158954634</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
         <v>1.295012675798237</v>
       </c>
-      <c r="M21" t="n">
+      <c r="P21" t="n">
+        <v>1.423912956510213</v>
+      </c>
+      <c r="Q21" t="n">
         <v>1.668889028806007</v>
       </c>
-      <c r="N21" t="n">
+      <c r="R21" t="n">
         <v>0.9237300000000001</v>
       </c>
-      <c r="O21" t="n">
+      <c r="S21" t="n">
         <v>0.7421078744088416</v>
       </c>
-      <c r="P21" t="n">
+      <c r="T21" t="n">
+        <v>1.913610823632234</v>
+      </c>
+      <c r="U21" t="n">
         <v>1.904022458784198</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="V21" t="n">
         <v>0.69143</v>
       </c>
     </row>
@@ -2704,45 +3299,60 @@
         <v>0.8658536585365854</v>
       </c>
       <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
         <v>0.4634146341463415</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>0.01575</v>
       </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
       <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.6935483870967742</v>
+      </c>
+      <c r="I22" t="n">
         <v>0.3467741935483871</v>
       </c>
-      <c r="H22" t="n">
+      <c r="J22" t="n">
         <v>0.43307</v>
       </c>
-      <c r="I22" t="n">
+      <c r="K22" t="n">
         <v>4.229330853807493</v>
       </c>
-      <c r="J22" t="n">
+      <c r="L22" t="n">
+        <v>17.57822176448747</v>
+      </c>
+      <c r="M22" t="n">
         <v>14.7036031414879</v>
       </c>
-      <c r="K22" t="n">
+      <c r="N22" t="n">
         <v>218.79106</v>
       </c>
-      <c r="L22" t="n">
+      <c r="O22" t="n">
         <v>1.080788708430336</v>
       </c>
-      <c r="M22" t="n">
+      <c r="P22" t="n">
+        <v>1.548677625841293</v>
+      </c>
+      <c r="Q22" t="n">
         <v>1.457116500845755</v>
       </c>
-      <c r="N22" t="n">
+      <c r="R22" t="n">
         <v>1.00467</v>
       </c>
-      <c r="O22" t="n">
+      <c r="S22" t="n">
         <v>1.046962522759265</v>
       </c>
-      <c r="P22" t="n">
+      <c r="T22" t="n">
+        <v>1.01598911148976</v>
+      </c>
+      <c r="U22" t="n">
         <v>1.087848958472849</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="V22" t="n">
         <v>0.83362</v>
       </c>
     </row>
@@ -2761,45 +3371,60 @@
         <v>0.6881720430107527</v>
       </c>
       <c r="D23" t="n">
+        <v>0.01075268817204301</v>
+      </c>
+      <c r="E23" t="n">
         <v>0.5268817204301075</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>0.00709</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>0.08888888888888889</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
+        <v>0.6962962962962963</v>
+      </c>
+      <c r="I23" t="n">
         <v>0.2148148148148148</v>
       </c>
-      <c r="H23" t="n">
+      <c r="J23" t="n">
         <v>0.39007</v>
       </c>
-      <c r="I23" t="n">
+      <c r="K23" t="n">
         <v>11.07566730746037</v>
       </c>
-      <c r="J23" t="n">
+      <c r="L23" t="n">
+        <v>17.99494713437912</v>
+      </c>
+      <c r="M23" t="n">
         <v>10.40046208079448</v>
       </c>
-      <c r="K23" t="n">
+      <c r="N23" t="n">
         <v>256.4209</v>
       </c>
-      <c r="L23" t="n">
+      <c r="O23" t="n">
         <v>1.954278930868299</v>
       </c>
-      <c r="M23" t="n">
+      <c r="P23" t="n">
+        <v>4.736892304419908</v>
+      </c>
+      <c r="Q23" t="n">
         <v>3.240170629016954</v>
       </c>
-      <c r="N23" t="n">
+      <c r="R23" t="n">
         <v>3.07294</v>
       </c>
-      <c r="O23" t="n">
+      <c r="S23" t="n">
         <v>1.370850418397646</v>
       </c>
-      <c r="P23" t="n">
+      <c r="T23" t="n">
+        <v>1.384141127196043</v>
+      </c>
+      <c r="U23" t="n">
         <v>1.410785663263062</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="V23" t="n">
         <v>0.97609</v>
       </c>
     </row>
@@ -2818,45 +3443,60 @@
         <v>0.7755102040816326</v>
       </c>
       <c r="D24" t="n">
+        <v>0.3265306122448979</v>
+      </c>
+      <c r="E24" t="n">
         <v>0.1224489795918367</v>
       </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.06329113924050633</v>
+      </c>
+      <c r="I24" t="n">
         <v>0.0759493670886076</v>
       </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>3.850451811752853</v>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
+        <v>6.757151499919122</v>
+      </c>
+      <c r="M24" t="n">
         <v>18.29526789578733</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
         <v>0.9779373575798956</v>
       </c>
-      <c r="M24" t="n">
+      <c r="P24" t="n">
+        <v>1.872826681146451</v>
+      </c>
+      <c r="Q24" t="n">
         <v>1.612281825808467</v>
       </c>
-      <c r="N24" t="n">
+      <c r="R24" t="n">
         <v>1.23937</v>
       </c>
-      <c r="O24" t="n">
+      <c r="S24" t="n">
         <v>0.5013240016831833</v>
       </c>
-      <c r="P24" t="n">
+      <c r="T24" t="n">
+        <v>0.5388554461565965</v>
+      </c>
+      <c r="U24" t="n">
         <v>0.5297634425894687</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="V24" t="n">
         <v>0.3409</v>
       </c>
     </row>
@@ -2875,45 +3515,60 @@
         <v>0.6774193548387096</v>
       </c>
       <c r="D25" t="n">
+        <v>0.2258064516129032</v>
+      </c>
+      <c r="E25" t="n">
         <v>0.3655913978494624</v>
       </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
       <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
         <v>0.007692307692307693</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
+        <v>0.3076923076923077</v>
+      </c>
+      <c r="I25" t="n">
         <v>0.4230769230769231</v>
       </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
         <v>5.826722210933315</v>
       </c>
-      <c r="J25" t="n">
+      <c r="L25" t="n">
+        <v>9.892823132979581</v>
+      </c>
+      <c r="M25" t="n">
         <v>14.6712575203888</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
         <v>1.619200934786085</v>
       </c>
-      <c r="M25" t="n">
+      <c r="P25" t="n">
+        <v>3.562178717583679</v>
+      </c>
+      <c r="Q25" t="n">
         <v>2.389407819654369</v>
       </c>
-      <c r="N25" t="n">
+      <c r="R25" t="n">
         <v>2.34845</v>
       </c>
-      <c r="O25" t="n">
+      <c r="S25" t="n">
         <v>0.7429645614440452</v>
       </c>
-      <c r="P25" t="n">
+      <c r="T25" t="n">
+        <v>1.047096700905661</v>
+      </c>
+      <c r="U25" t="n">
         <v>1.8011542393133</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="V25" t="n">
         <v>0.67742</v>
       </c>
     </row>
@@ -2932,45 +3587,60 @@
         <v>0.6404494382022472</v>
       </c>
       <c r="D26" t="n">
+        <v>0.5168539325842697</v>
+      </c>
+      <c r="E26" t="n">
         <v>0.1910112359550562</v>
       </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
       <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
         <v>0.09302325581395349</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
+        <v>0.2403100775193799</v>
+      </c>
+      <c r="I26" t="n">
         <v>0.4186046511627907</v>
       </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
         <v>34.49107132873646</v>
       </c>
-      <c r="J26" t="n">
+      <c r="L26" t="n">
+        <v>10.80943273534367</v>
+      </c>
+      <c r="M26" t="n">
         <v>12.25362166661118</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
         <v>1.616903838332878</v>
       </c>
-      <c r="M26" t="n">
+      <c r="P26" t="n">
+        <v>3.620108184108776</v>
+      </c>
+      <c r="Q26" t="n">
         <v>2.651209299827381</v>
       </c>
-      <c r="N26" t="n">
+      <c r="R26" t="n">
         <v>2.34845</v>
       </c>
-      <c r="O26" t="n">
+      <c r="S26" t="n">
         <v>1.717747809022253</v>
       </c>
-      <c r="P26" t="n">
+      <c r="T26" t="n">
+        <v>1.806696070515576</v>
+      </c>
+      <c r="U26" t="n">
         <v>1.759708834405026</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="V26" t="n">
         <v>0.61188</v>
       </c>
     </row>
@@ -2989,45 +3659,60 @@
         <v>0.6290322580645161</v>
       </c>
       <c r="D27" t="n">
+        <v>0.6935483870967742</v>
+      </c>
+      <c r="E27" t="n">
         <v>0.4354838709677419</v>
       </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
       <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
         <v>0.02727272727272727</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="I27" t="n">
         <v>0.1727272727272727</v>
       </c>
-      <c r="H27" t="n">
+      <c r="J27" t="n">
         <v>0.09009</v>
       </c>
-      <c r="I27" t="n">
+      <c r="K27" t="n">
         <v>7.505001391078864</v>
       </c>
-      <c r="J27" t="n">
+      <c r="L27" t="n">
+        <v>12.14269055325155</v>
+      </c>
+      <c r="M27" t="n">
         <v>20.79552379580807</v>
       </c>
-      <c r="K27" t="n">
+      <c r="N27" t="n">
         <v>87.09361</v>
       </c>
-      <c r="L27" t="n">
+      <c r="O27" t="n">
         <v>1.27297092256118</v>
       </c>
-      <c r="M27" t="n">
+      <c r="P27" t="n">
+        <v>3.607378951326283</v>
+      </c>
+      <c r="Q27" t="n">
         <v>2.023998294581387</v>
       </c>
-      <c r="N27" t="n">
+      <c r="R27" t="n">
         <v>2.51936</v>
       </c>
-      <c r="O27" t="n">
+      <c r="S27" t="n">
         <v>0.742143252725923</v>
       </c>
-      <c r="P27" t="n">
+      <c r="T27" t="n">
+        <v>0.9386484944868703</v>
+      </c>
+      <c r="U27" t="n">
         <v>0.9425089223540017</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="V27" t="n">
         <v>0.69025</v>
       </c>
     </row>
@@ -3046,45 +3731,60 @@
         <v>0.5223880597014925</v>
       </c>
       <c r="D28" t="n">
+        <v>0.582089552238806</v>
+      </c>
+      <c r="E28" t="n">
         <v>0.4776119402985075</v>
       </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
       <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
         <v>0.1071428571428571</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I28" t="n">
         <v>0.2053571428571428</v>
       </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
         <v>11.44407787804499</v>
       </c>
-      <c r="J28" t="n">
+      <c r="L28" t="n">
+        <v>11.0820457929642</v>
+      </c>
+      <c r="M28" t="n">
         <v>28.43171301776546</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
         <v>1.342638378391138</v>
       </c>
-      <c r="M28" t="n">
+      <c r="P28" t="n">
+        <v>2.987312484156669</v>
+      </c>
+      <c r="Q28" t="n">
         <v>2.008124644291674</v>
       </c>
-      <c r="N28" t="n">
+      <c r="R28" t="n">
         <v>1.90415</v>
       </c>
-      <c r="O28" t="n">
+      <c r="S28" t="n">
         <v>0.5961672182586848</v>
       </c>
-      <c r="P28" t="n">
+      <c r="T28" t="n">
+        <v>1.277573453058124</v>
+      </c>
+      <c r="U28" t="n">
         <v>1.093723004345007</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="V28" t="n">
         <v>0.39401</v>
       </c>
     </row>
@@ -3103,45 +3803,60 @@
         <v>0.5873015873015873</v>
       </c>
       <c r="D29" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="E29" t="n">
         <v>0.4126984126984127</v>
       </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
       <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
         <v>0.08208955223880597</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
+        <v>0.2164179104477612</v>
+      </c>
+      <c r="I29" t="n">
         <v>0.1492537313432836</v>
       </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
         <v>10.61297227288824</v>
       </c>
-      <c r="J29" t="n">
+      <c r="L29" t="n">
+        <v>11.80338998060597</v>
+      </c>
+      <c r="M29" t="n">
         <v>28.86519622067859</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
         <v>1.797457651278315</v>
       </c>
-      <c r="M29" t="n">
+      <c r="P29" t="n">
+        <v>2.142852376093303</v>
+      </c>
+      <c r="Q29" t="n">
         <v>1.913072579212308</v>
       </c>
-      <c r="N29" t="n">
+      <c r="R29" t="n">
         <v>1.41806</v>
       </c>
-      <c r="O29" t="n">
+      <c r="S29" t="n">
         <v>0.1766219990320586</v>
       </c>
-      <c r="P29" t="n">
+      <c r="T29" t="n">
+        <v>1.495638423823059</v>
+      </c>
+      <c r="U29" t="n">
         <v>0.6664713975780704</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="V29" t="n">
         <v>0.15356</v>
       </c>
     </row>
@@ -3160,45 +3875,60 @@
         <v>0.7096774193548387</v>
       </c>
       <c r="D30" t="n">
+        <v>0.3064516129032258</v>
+      </c>
+      <c r="E30" t="n">
         <v>0.3225806451612903</v>
       </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
       <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
         <v>0.05607476635514019</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
+        <v>0.3925233644859813</v>
+      </c>
+      <c r="I30" t="n">
         <v>0.2336448598130841</v>
       </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
         <v>53.34753443856344</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
+        <v>11.44631841569422</v>
+      </c>
+      <c r="M30" t="n">
         <v>27.92533788207854</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
         <v>1.954041348798044</v>
       </c>
-      <c r="M30" t="n">
+      <c r="P30" t="n">
+        <v>3.537746592383523</v>
+      </c>
+      <c r="Q30" t="n">
         <v>2.668259548434808</v>
       </c>
-      <c r="N30" t="n">
+      <c r="R30" t="n">
         <v>2.47073</v>
       </c>
-      <c r="O30" t="n">
+      <c r="S30" t="n">
         <v>0.6871128106518338</v>
       </c>
-      <c r="P30" t="n">
+      <c r="T30" t="n">
+        <v>1.630448457640536</v>
+      </c>
+      <c r="U30" t="n">
         <v>0.7185228255241937</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="V30" t="n">
         <v>1.08886</v>
       </c>
     </row>
@@ -3217,45 +3947,60 @@
         <v>0.7272727272727273</v>
       </c>
       <c r="D31" t="n">
+        <v>0.02727272727272727</v>
+      </c>
+      <c r="E31" t="n">
         <v>0.3818181818181818</v>
       </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
       <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
         <v>0.0625</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I31" t="n">
         <v>0.2788461538461539</v>
       </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
         <v>13.87537748739781</v>
       </c>
-      <c r="J31" t="n">
+      <c r="L31" t="n">
+        <v>37.63992458529604</v>
+      </c>
+      <c r="M31" t="n">
         <v>25.35213565504233</v>
       </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
         <v>1.367371832366053</v>
       </c>
-      <c r="M31" t="n">
+      <c r="P31" t="n">
+        <v>2.184875724225232</v>
+      </c>
+      <c r="Q31" t="n">
         <v>1.62618272336638</v>
       </c>
-      <c r="N31" t="n">
+      <c r="R31" t="n">
         <v>1.43833</v>
       </c>
-      <c r="O31" t="n">
+      <c r="S31" t="n">
         <v>0.573027257570511</v>
       </c>
-      <c r="P31" t="n">
+      <c r="T31" t="n">
+        <v>2.294040282383296</v>
+      </c>
+      <c r="U31" t="n">
         <v>0.6093144300431216</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="V31" t="n">
         <v>2.08395</v>
       </c>
     </row>
@@ -3274,45 +4019,60 @@
         <v>0.8440366972477065</v>
       </c>
       <c r="D32" t="n">
+        <v>0.05504587155963303</v>
+      </c>
+      <c r="E32" t="n">
         <v>0.4862385321100918</v>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>0.00694</v>
       </c>
-      <c r="F32" t="n">
+      <c r="G32" t="n">
         <v>0.0625</v>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
+        <v>0.4791666666666667</v>
+      </c>
+      <c r="I32" t="n">
         <v>0.3680555555555556</v>
       </c>
-      <c r="H32" t="n">
+      <c r="J32" t="n">
         <v>0.05556</v>
       </c>
-      <c r="I32" t="n">
+      <c r="K32" t="n">
         <v>11.68766737012383</v>
       </c>
-      <c r="J32" t="n">
+      <c r="L32" t="n">
+        <v>18.18998759935009</v>
+      </c>
+      <c r="M32" t="n">
         <v>18.6562734018291</v>
       </c>
-      <c r="K32" t="n">
+      <c r="N32" t="n">
         <v>45.66906</v>
       </c>
-      <c r="L32" t="n">
+      <c r="O32" t="n">
         <v>1.363801125971931</v>
       </c>
-      <c r="M32" t="n">
+      <c r="P32" t="n">
+        <v>2.464370001173771</v>
+      </c>
+      <c r="Q32" t="n">
         <v>1.946687006824114</v>
       </c>
-      <c r="N32" t="n">
+      <c r="R32" t="n">
         <v>1.69032</v>
       </c>
-      <c r="O32" t="n">
+      <c r="S32" t="n">
         <v>0.7605830535147979</v>
       </c>
-      <c r="P32" t="n">
+      <c r="T32" t="n">
+        <v>1.353529301914744</v>
+      </c>
+      <c r="U32" t="n">
         <v>1.215327784746927</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="V32" t="n">
         <v>1.62525</v>
       </c>
     </row>
@@ -3331,45 +4091,60 @@
         <v>0.3690476190476191</v>
       </c>
       <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
         <v>0.3095238095238095</v>
       </c>
-      <c r="E33" t="n">
-        <v>0</v>
-      </c>
       <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
         <v>0.4479166666666667</v>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
+        <v>0.8645833333333334</v>
+      </c>
+      <c r="I33" t="n">
         <v>0.375</v>
       </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
         <v>21.68822418862982</v>
       </c>
-      <c r="J33" t="n">
+      <c r="L33" t="n">
+        <v>45.35789662041155</v>
+      </c>
+      <c r="M33" t="n">
         <v>18.4456501820265</v>
       </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
         <v>1.359144658976586</v>
       </c>
-      <c r="M33" t="n">
+      <c r="P33" t="n">
+        <v>1.724696504707047</v>
+      </c>
+      <c r="Q33" t="n">
         <v>1.616276870967141</v>
       </c>
-      <c r="N33" t="n">
+      <c r="R33" t="n">
         <v>1.09934</v>
       </c>
-      <c r="O33" t="n">
+      <c r="S33" t="n">
         <v>0.6122692465166779</v>
       </c>
-      <c r="P33" t="n">
+      <c r="T33" t="n">
+        <v>0.9006300995438287</v>
+      </c>
+      <c r="U33" t="n">
         <v>0.7417912639562905</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="V33" t="n">
         <v>0.82201</v>
       </c>
     </row>
@@ -3391,42 +4166,57 @@
         <v>0.2666666666666667</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
         <v>0.05714285714285714</v>
       </c>
-      <c r="G34" t="n">
+      <c r="H34" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I34" t="n">
         <v>0.4571428571428571</v>
       </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
         <v>14.85103853349822</v>
       </c>
-      <c r="J34" t="n">
+      <c r="L34" t="n">
+        <v>10.01287805263151</v>
+      </c>
+      <c r="M34" t="n">
         <v>17.38404340164704</v>
       </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
         <v>1.049032001112261</v>
       </c>
-      <c r="M34" t="n">
+      <c r="P34" t="n">
+        <v>1.656220369515699</v>
+      </c>
+      <c r="Q34" t="n">
         <v>1.531206893427911</v>
       </c>
-      <c r="N34" t="n">
+      <c r="R34" t="n">
         <v>1.13373</v>
       </c>
-      <c r="O34" t="n">
+      <c r="S34" t="n">
         <v>0.4644860596224726</v>
       </c>
-      <c r="P34" t="n">
+      <c r="T34" t="n">
+        <v>1.290844449591673</v>
+      </c>
+      <c r="U34" t="n">
         <v>0.7869602297732563</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="V34" t="n">
         <v>1.49084</v>
       </c>
     </row>
@@ -3445,45 +4235,60 @@
         <v>0.7127659574468085</v>
       </c>
       <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
         <v>0.3085106382978723</v>
       </c>
-      <c r="E35" t="n">
-        <v>0</v>
-      </c>
       <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
         <v>0.1555555555555556</v>
       </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
+        <v>0.7111111111111111</v>
+      </c>
+      <c r="I35" t="n">
         <v>0.4518518518518518</v>
       </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
         <v>10.86266693376921</v>
       </c>
-      <c r="J35" t="n">
+      <c r="L35" t="n">
+        <v>90.46626616546556</v>
+      </c>
+      <c r="M35" t="n">
         <v>43.31822562711761</v>
       </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
         <v>1.241297040988529</v>
       </c>
-      <c r="M35" t="n">
+      <c r="P35" t="n">
+        <v>2.402587327173854</v>
+      </c>
+      <c r="Q35" t="n">
         <v>1.630258618092435</v>
       </c>
-      <c r="N35" t="n">
+      <c r="R35" t="n">
         <v>1.59679</v>
       </c>
-      <c r="O35" t="n">
+      <c r="S35" t="n">
         <v>0.479877048263687</v>
       </c>
-      <c r="P35" t="n">
+      <c r="T35" t="n">
+        <v>1.565795090161652</v>
+      </c>
+      <c r="U35" t="n">
         <v>1.614796891258949</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="V35" t="n">
         <v>1.7721</v>
       </c>
     </row>
@@ -3502,45 +4307,60 @@
         <v>0.7169811320754716</v>
       </c>
       <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
         <v>0.03773584905660377</v>
       </c>
-      <c r="E36" t="n">
+      <c r="F36" t="n">
         <v>0.009520000000000001</v>
       </c>
-      <c r="F36" t="n">
+      <c r="G36" t="n">
         <v>0.1047619047619048</v>
       </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
+        <v>0.5333333333333333</v>
+      </c>
+      <c r="I36" t="n">
         <v>0.5619047619047619</v>
       </c>
-      <c r="H36" t="n">
+      <c r="J36" t="n">
         <v>0.18095</v>
       </c>
-      <c r="I36" t="n">
+      <c r="K36" t="n">
         <v>10.21912335658691</v>
       </c>
-      <c r="J36" t="n">
+      <c r="L36" t="n">
+        <v>97.72935427813795</v>
+      </c>
+      <c r="M36" t="n">
         <v>27.58990696575184</v>
       </c>
-      <c r="K36" t="n">
+      <c r="N36" t="n">
         <v>58.94553</v>
       </c>
-      <c r="L36" t="n">
+      <c r="O36" t="n">
         <v>1.104971314567135</v>
       </c>
-      <c r="M36" t="n">
+      <c r="P36" t="n">
+        <v>2.606734602466808</v>
+      </c>
+      <c r="Q36" t="n">
         <v>1.658275032410497</v>
       </c>
-      <c r="N36" t="n">
+      <c r="R36" t="n">
         <v>1.73247</v>
       </c>
-      <c r="O36" t="n">
+      <c r="S36" t="n">
         <v>0.4581237279804456</v>
       </c>
-      <c r="P36" t="n">
+      <c r="T36" t="n">
+        <v>0.6575109145149358</v>
+      </c>
+      <c r="U36" t="n">
         <v>0.6031884729962481</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="V36" t="n">
         <v>0.60945</v>
       </c>
     </row>
@@ -3559,45 +4379,60 @@
         <v>0.6</v>
       </c>
       <c r="D37" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="E37" t="n">
         <v>0.5272727272727272</v>
       </c>
-      <c r="E37" t="n">
-        <v>0</v>
-      </c>
       <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
         <v>0.09433962264150944</v>
       </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
+        <v>0.4811320754716981</v>
+      </c>
+      <c r="I37" t="n">
         <v>0.3396226415094339</v>
       </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
         <v>8.832011043151152</v>
       </c>
-      <c r="J37" t="n">
+      <c r="L37" t="n">
+        <v>69.25888326370523</v>
+      </c>
+      <c r="M37" t="n">
         <v>29.44350946803073</v>
       </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
         <v>1.288138091850065</v>
       </c>
-      <c r="M37" t="n">
+      <c r="P37" t="n">
+        <v>2.617967827855063</v>
+      </c>
+      <c r="Q37" t="n">
         <v>1.733763726897135</v>
       </c>
-      <c r="N37" t="n">
+      <c r="R37" t="n">
         <v>1.73247</v>
       </c>
-      <c r="O37" t="n">
+      <c r="S37" t="n">
         <v>1.009209836543102</v>
       </c>
-      <c r="P37" t="n">
+      <c r="T37" t="n">
+        <v>1.059695089559394</v>
+      </c>
+      <c r="U37" t="n">
         <v>1.079901017648816</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="V37" t="n">
         <v>1.19614</v>
       </c>
     </row>
@@ -3616,45 +4451,60 @@
         <v>0.863013698630137</v>
       </c>
       <c r="D38" t="n">
+        <v>0.2328767123287671</v>
+      </c>
+      <c r="E38" t="n">
         <v>0.0547945205479452</v>
       </c>
-      <c r="E38" t="n">
-        <v>0</v>
-      </c>
       <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
         <v>0.07333333333333333</v>
       </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="I38" t="n">
         <v>0.6466666666666666</v>
       </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
         <v>9.493949266300305</v>
       </c>
-      <c r="J38" t="n">
+      <c r="L38" t="n">
+        <v>11.23046491028162</v>
+      </c>
+      <c r="M38" t="n">
         <v>31.60571098863247</v>
       </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
         <v>0.852711916319936</v>
       </c>
-      <c r="M38" t="n">
+      <c r="P38" t="n">
+        <v>1.453300321070025</v>
+      </c>
+      <c r="Q38" t="n">
         <v>1.205341043511685</v>
       </c>
-      <c r="N38" t="n">
+      <c r="R38" t="n">
         <v>0.93864</v>
       </c>
-      <c r="O38" t="n">
+      <c r="S38" t="n">
         <v>0.4740139603044363</v>
       </c>
-      <c r="P38" t="n">
+      <c r="T38" t="n">
+        <v>0.7285307733276911</v>
+      </c>
+      <c r="U38" t="n">
         <v>0.6492469228807261</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="V38" t="n">
         <v>0.7511</v>
       </c>
     </row>
@@ -3673,45 +4523,60 @@
         <v>0.8450704225352113</v>
       </c>
       <c r="D39" t="n">
+        <v>0.07042253521126761</v>
+      </c>
+      <c r="E39" t="n">
         <v>0.1549295774647887</v>
       </c>
-      <c r="E39" t="n">
-        <v>0</v>
-      </c>
       <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
         <v>0.04838709677419355</v>
       </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
+        <v>0.3709677419354839</v>
+      </c>
+      <c r="I39" t="n">
         <v>0.5564516129032258</v>
       </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
         <v>10.30761313141118</v>
       </c>
-      <c r="J39" t="n">
+      <c r="L39" t="n">
+        <v>10.83677777333505</v>
+      </c>
+      <c r="M39" t="n">
         <v>16.93910628152885</v>
       </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
         <v>1.25368778297571</v>
       </c>
-      <c r="M39" t="n">
+      <c r="P39" t="n">
+        <v>2.122155024446051</v>
+      </c>
+      <c r="Q39" t="n">
         <v>1.646365871787296</v>
       </c>
-      <c r="N39" t="n">
+      <c r="R39" t="n">
         <v>1.37063</v>
       </c>
-      <c r="O39" t="n">
+      <c r="S39" t="n">
         <v>0.5320410496078745</v>
       </c>
-      <c r="P39" t="n">
+      <c r="T39" t="n">
+        <v>1.262481441887706</v>
+      </c>
+      <c r="U39" t="n">
         <v>1.26894668639185</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="V39" t="n">
         <v>1.36934</v>
       </c>
     </row>
@@ -3730,45 +4595,60 @@
         <v>0.9504132231404959</v>
       </c>
       <c r="D40" t="n">
+        <v>0.008264462809917356</v>
+      </c>
+      <c r="E40" t="n">
         <v>0.2644628099173554</v>
       </c>
-      <c r="E40" t="n">
-        <v>0</v>
-      </c>
       <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
         <v>0.02298850574712644</v>
       </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
+        <v>0.7068965517241379</v>
+      </c>
+      <c r="I40" t="n">
         <v>0.5172413793103449</v>
       </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
         <v>6.982575574274628</v>
       </c>
-      <c r="J40" t="n">
+      <c r="L40" t="n">
+        <v>50.41034725172952</v>
+      </c>
+      <c r="M40" t="n">
         <v>12.94406279522447</v>
       </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="n">
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
         <v>1.368529131867075</v>
       </c>
-      <c r="M40" t="n">
+      <c r="P40" t="n">
+        <v>2.266400000134376</v>
+      </c>
+      <c r="Q40" t="n">
         <v>1.826588470177358</v>
       </c>
-      <c r="N40" t="n">
+      <c r="R40" t="n">
         <v>1.54161</v>
       </c>
-      <c r="O40" t="n">
+      <c r="S40" t="n">
         <v>1.636378745208094</v>
       </c>
-      <c r="P40" t="n">
+      <c r="T40" t="n">
+        <v>1.649547712031842</v>
+      </c>
+      <c r="U40" t="n">
         <v>1.650406309436122</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="V40" t="n">
         <v>1.69171</v>
       </c>
     </row>
@@ -3787,45 +4667,60 @@
         <v>0.9206349206349206</v>
       </c>
       <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="E41" t="n">
-        <v>0</v>
-      </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.5483870967741935</v>
+      </c>
+      <c r="I41" t="n">
         <v>0.1693548387096774</v>
       </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
         <v>2.864409768497302</v>
       </c>
-      <c r="J41" t="n">
+      <c r="L41" t="n">
+        <v>46.79204573448805</v>
+      </c>
+      <c r="M41" t="n">
         <v>12.34841560365823</v>
       </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="n">
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
         <v>0.8470797902201102</v>
       </c>
-      <c r="M41" t="n">
+      <c r="P41" t="n">
+        <v>1.557316428955656</v>
+      </c>
+      <c r="Q41" t="n">
         <v>1.113292959490537</v>
       </c>
-      <c r="N41" t="n">
+      <c r="R41" t="n">
         <v>1.01027</v>
       </c>
-      <c r="O41" t="n">
+      <c r="S41" t="n">
         <v>1.030930624651113</v>
       </c>
-      <c r="P41" t="n">
+      <c r="T41" t="n">
+        <v>0.9857012692976862</v>
+      </c>
+      <c r="U41" t="n">
         <v>0.9828276037434964</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="V41" t="n">
         <v>1.02196</v>
       </c>
     </row>
@@ -3844,45 +4739,60 @@
         <v>0.8645833333333334</v>
       </c>
       <c r="D42" t="n">
+        <v>0.1354166666666667</v>
+      </c>
+      <c r="E42" t="n">
         <v>0.5</v>
       </c>
-      <c r="E42" t="n">
-        <v>0</v>
-      </c>
       <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
         <v>0.02542372881355932</v>
       </c>
-      <c r="G42" t="n">
+      <c r="H42" t="n">
+        <v>0.7627118644067796</v>
+      </c>
+      <c r="I42" t="n">
         <v>0.3050847457627119</v>
       </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
         <v>13.11567853739846</v>
       </c>
-      <c r="J42" t="n">
+      <c r="L42" t="n">
+        <v>45.31053863793514</v>
+      </c>
+      <c r="M42" t="n">
         <v>12.88770812648746</v>
       </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="n">
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
         <v>0.8809426282577797</v>
       </c>
-      <c r="M42" t="n">
+      <c r="P42" t="n">
+        <v>0.8930253528596356</v>
+      </c>
+      <c r="Q42" t="n">
         <v>0.9703614315049904</v>
       </c>
-      <c r="N42" t="n">
+      <c r="R42" t="n">
         <v>0.6113</v>
       </c>
-      <c r="O42" t="n">
+      <c r="S42" t="n">
         <v>0.5657206854922161</v>
       </c>
-      <c r="P42" t="n">
+      <c r="T42" t="n">
+        <v>1.072363829583318</v>
+      </c>
+      <c r="U42" t="n">
         <v>0.9856126695726666</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="V42" t="n">
         <v>1.29826</v>
       </c>
     </row>
@@ -3901,45 +4811,60 @@
         <v>0.781021897810219</v>
       </c>
       <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
         <v>0.343065693430657</v>
       </c>
-      <c r="E43" t="n">
-        <v>0</v>
-      </c>
       <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
         <v>0.09042553191489362</v>
       </c>
-      <c r="G43" t="n">
+      <c r="H43" t="n">
+        <v>0.8776595744680851</v>
+      </c>
+      <c r="I43" t="n">
         <v>0.7340425531914894</v>
       </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
         <v>14.81906720986315</v>
       </c>
-      <c r="J43" t="n">
+      <c r="L43" t="n">
+        <v>47.47310717400088</v>
+      </c>
+      <c r="M43" t="n">
         <v>18.99255917083862</v>
       </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
         <v>1.07775743850009</v>
       </c>
-      <c r="M43" t="n">
+      <c r="P43" t="n">
+        <v>1.491163438140183</v>
+      </c>
+      <c r="Q43" t="n">
         <v>1.27094924697229</v>
       </c>
-      <c r="N43" t="n">
+      <c r="R43" t="n">
         <v>1.02074</v>
       </c>
-      <c r="O43" t="n">
+      <c r="S43" t="n">
         <v>0.5348300443079016</v>
       </c>
-      <c r="P43" t="n">
+      <c r="T43" t="n">
+        <v>1.226781853871494</v>
+      </c>
+      <c r="U43" t="n">
         <v>1.309581036887211</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="V43" t="n">
         <v>1.50477</v>
       </c>
     </row>
@@ -3958,45 +4883,60 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
         <v>0.5064935064935064</v>
       </c>
-      <c r="E44" t="n">
-        <v>0</v>
-      </c>
       <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
         <v>0.06666666666666667</v>
       </c>
-      <c r="G44" t="n">
+      <c r="H44" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I44" t="n">
         <v>0.2416666666666667</v>
       </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
         <v>26.59652187157186</v>
       </c>
-      <c r="J44" t="n">
+      <c r="L44" t="n">
+        <v>44.96118720390773</v>
+      </c>
+      <c r="M44" t="n">
         <v>41.14813860805462</v>
       </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
         <v>1.216919640075743</v>
       </c>
-      <c r="M44" t="n">
+      <c r="P44" t="n">
+        <v>2.300297807346464</v>
+      </c>
+      <c r="Q44" t="n">
         <v>1.772278031514434</v>
       </c>
-      <c r="N44" t="n">
+      <c r="R44" t="n">
         <v>1.57462</v>
       </c>
-      <c r="O44" t="n">
+      <c r="S44" t="n">
         <v>0.4582914476642666</v>
       </c>
-      <c r="P44" t="n">
+      <c r="T44" t="n">
+        <v>1.195252523949747</v>
+      </c>
+      <c r="U44" t="n">
         <v>1.276706817047761</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="V44" t="n">
         <v>1.36271</v>
       </c>
     </row>
@@ -4015,45 +4955,60 @@
         <v>0.845360824742268</v>
       </c>
       <c r="D45" t="n">
+        <v>0.2061855670103093</v>
+      </c>
+      <c r="E45" t="n">
         <v>0.2164948453608248</v>
       </c>
-      <c r="E45" t="n">
+      <c r="F45" t="n">
         <v>0.01587</v>
       </c>
-      <c r="F45" t="n">
+      <c r="G45" t="n">
         <v>0.03174603174603174</v>
       </c>
-      <c r="G45" t="n">
+      <c r="H45" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="I45" t="n">
         <v>0.5158730158730159</v>
       </c>
-      <c r="H45" t="n">
+      <c r="J45" t="n">
         <v>0.02381</v>
       </c>
-      <c r="I45" t="n">
+      <c r="K45" t="n">
         <v>5.947987355441398</v>
       </c>
-      <c r="J45" t="n">
+      <c r="L45" t="n">
+        <v>11.54361412900618</v>
+      </c>
+      <c r="M45" t="n">
         <v>38.5997516821119</v>
       </c>
-      <c r="K45" t="n">
+      <c r="N45" t="n">
         <v>7.5222</v>
       </c>
-      <c r="L45" t="n">
+      <c r="O45" t="n">
         <v>1.170114164004421</v>
       </c>
-      <c r="M45" t="n">
+      <c r="P45" t="n">
+        <v>5.076061667964132</v>
+      </c>
+      <c r="Q45" t="n">
         <v>1.718852044109206</v>
       </c>
-      <c r="N45" t="n">
+      <c r="R45" t="n">
         <v>3.35915</v>
       </c>
-      <c r="O45" t="n">
+      <c r="S45" t="n">
         <v>0.5056571852582697</v>
       </c>
-      <c r="P45" t="n">
+      <c r="T45" t="n">
+        <v>1.772809905013914</v>
+      </c>
+      <c r="U45" t="n">
         <v>0.7073818931395617</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="V45" t="n">
         <v>0.99177</v>
       </c>
     </row>
@@ -4072,45 +5027,60 @@
         <v>0.7708333333333334</v>
       </c>
       <c r="D46" t="n">
+        <v>0.3958333333333333</v>
+      </c>
+      <c r="E46" t="n">
         <v>0.2916666666666667</v>
       </c>
-      <c r="E46" t="n">
-        <v>0</v>
-      </c>
       <c r="F46" t="n">
         <v>0</v>
       </c>
       <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.007874015748031496</v>
+      </c>
+      <c r="I46" t="n">
         <v>0.5275590551181102</v>
       </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
         <v>3.297448992170466</v>
       </c>
-      <c r="J46" t="n">
+      <c r="L46" t="n">
+        <v>11.18564091885482</v>
+      </c>
+      <c r="M46" t="n">
         <v>16.58143860109612</v>
       </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
         <v>1.040773662216431</v>
       </c>
-      <c r="M46" t="n">
+      <c r="P46" t="n">
+        <v>4.809834285667971</v>
+      </c>
+      <c r="Q46" t="n">
         <v>1.548528388690794</v>
       </c>
-      <c r="N46" t="n">
+      <c r="R46" t="n">
         <v>3.35915</v>
       </c>
-      <c r="O46" t="n">
+      <c r="S46" t="n">
         <v>1.704235217646096</v>
       </c>
-      <c r="P46" t="n">
+      <c r="T46" t="n">
+        <v>1.834255853497264</v>
+      </c>
+      <c r="U46" t="n">
         <v>1.76376939826926</v>
       </c>
-      <c r="Q46" t="n">
+      <c r="V46" t="n">
         <v>2.21639</v>
       </c>
     </row>
@@ -4129,45 +5099,60 @@
         <v>0.6438356164383562</v>
       </c>
       <c r="D47" t="n">
+        <v>0.1232876712328767</v>
+      </c>
+      <c r="E47" t="n">
         <v>0.0958904109589041</v>
       </c>
-      <c r="E47" t="n">
-        <v>0</v>
-      </c>
       <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
         <v>0.1724137931034483</v>
       </c>
-      <c r="G47" t="n">
+      <c r="H47" t="n">
+        <v>0.4827586206896552</v>
+      </c>
+      <c r="I47" t="n">
         <v>0.6206896551724138</v>
       </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="n">
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
         <v>12.77891420105633</v>
       </c>
-      <c r="J47" t="n">
+      <c r="L47" t="n">
+        <v>10.20912436557519</v>
+      </c>
+      <c r="M47" t="n">
         <v>27.92102230461759</v>
       </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
         <v>1.474947031505469</v>
       </c>
-      <c r="M47" t="n">
+      <c r="P47" t="n">
+        <v>4.445202495291326</v>
+      </c>
+      <c r="Q47" t="n">
         <v>2.257902486426277</v>
       </c>
-      <c r="N47" t="n">
+      <c r="R47" t="n">
         <v>2.94167</v>
       </c>
-      <c r="O47" t="n">
+      <c r="S47" t="n">
         <v>0.6665479859605434</v>
       </c>
-      <c r="P47" t="n">
+      <c r="T47" t="n">
+        <v>1.459868436860006</v>
+      </c>
+      <c r="U47" t="n">
         <v>1.353095903573619</v>
       </c>
-      <c r="Q47" t="n">
+      <c r="V47" t="n">
         <v>1.60896</v>
       </c>
     </row>
@@ -4186,45 +5171,60 @@
         <v>0.7938144329896907</v>
       </c>
       <c r="D48" t="n">
+        <v>0.3092783505154639</v>
+      </c>
+      <c r="E48" t="n">
         <v>0.2474226804123711</v>
       </c>
-      <c r="E48" t="n">
-        <v>0</v>
-      </c>
       <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
         <v>0.0916030534351145</v>
       </c>
-      <c r="G48" t="n">
+      <c r="H48" t="n">
+        <v>0.5190839694656488</v>
+      </c>
+      <c r="I48" t="n">
         <v>0.5725190839694656</v>
       </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
         <v>6.630259625639203</v>
       </c>
-      <c r="J48" t="n">
+      <c r="L48" t="n">
+        <v>9.716893614799682</v>
+      </c>
+      <c r="M48" t="n">
         <v>15.6697082610916</v>
       </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
         <v>1.427014362126045</v>
       </c>
-      <c r="M48" t="n">
+      <c r="P48" t="n">
+        <v>2.774937797188087</v>
+      </c>
+      <c r="Q48" t="n">
         <v>1.739301661267125</v>
       </c>
-      <c r="N48" t="n">
+      <c r="R48" t="n">
         <v>1.80017</v>
       </c>
-      <c r="O48" t="n">
+      <c r="S48" t="n">
         <v>0.6692323362887259</v>
       </c>
-      <c r="P48" t="n">
+      <c r="T48" t="n">
+        <v>2.08395061112776</v>
+      </c>
+      <c r="U48" t="n">
         <v>0.6143572560714302</v>
       </c>
-      <c r="Q48" t="n">
+      <c r="V48" t="n">
         <v>0.91855</v>
       </c>
     </row>
@@ -4243,45 +5243,60 @@
         <v>0.8672566371681416</v>
       </c>
       <c r="D49" t="n">
+        <v>0.1504424778761062</v>
+      </c>
+      <c r="E49" t="n">
         <v>0.2743362831858407</v>
       </c>
-      <c r="E49" t="n">
+      <c r="F49" t="n">
         <v>0.01408</v>
       </c>
-      <c r="F49" t="n">
+      <c r="G49" t="n">
         <v>0.04929577464788732</v>
       </c>
-      <c r="G49" t="n">
+      <c r="H49" t="n">
+        <v>0.1830985915492958</v>
+      </c>
+      <c r="I49" t="n">
         <v>0.5704225352112676</v>
       </c>
-      <c r="H49" t="n">
+      <c r="J49" t="n">
         <v>0.07042</v>
       </c>
-      <c r="I49" t="n">
+      <c r="K49" t="n">
         <v>7.309787742413587</v>
       </c>
-      <c r="J49" t="n">
+      <c r="L49" t="n">
+        <v>14.34537801318646</v>
+      </c>
+      <c r="M49" t="n">
         <v>19.52077912950138</v>
       </c>
-      <c r="K49" t="n">
+      <c r="N49" t="n">
         <v>49.89262</v>
       </c>
-      <c r="L49" t="n">
+      <c r="O49" t="n">
         <v>1.34891317585904</v>
       </c>
-      <c r="M49" t="n">
+      <c r="P49" t="n">
+        <v>3.733694004412728</v>
+      </c>
+      <c r="Q49" t="n">
         <v>2.078459500262161</v>
       </c>
-      <c r="N49" t="n">
+      <c r="R49" t="n">
         <v>2.47082</v>
       </c>
-      <c r="O49" t="n">
+      <c r="S49" t="n">
         <v>0.3643661052099934</v>
       </c>
-      <c r="P49" t="n">
+      <c r="T49" t="n">
+        <v>1.789698957184121</v>
+      </c>
+      <c r="U49" t="n">
         <v>0.5376800532142459</v>
       </c>
-      <c r="Q49" t="n">
+      <c r="V49" t="n">
         <v>0.30481</v>
       </c>
     </row>
@@ -4300,45 +5315,60 @@
         <v>0.8823529411764706</v>
       </c>
       <c r="D50" t="n">
+        <v>0.08823529411764706</v>
+      </c>
+      <c r="E50" t="n">
         <v>0.3676470588235294</v>
       </c>
-      <c r="E50" t="n">
-        <v>0</v>
-      </c>
       <c r="F50" t="n">
         <v>0</v>
       </c>
       <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.6391752577319587</v>
+      </c>
+      <c r="I50" t="n">
         <v>0.3402061855670103</v>
       </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="n">
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
         <v>4.159187463107322</v>
       </c>
-      <c r="J50" t="n">
+      <c r="L50" t="n">
+        <v>18.86545825237236</v>
+      </c>
+      <c r="M50" t="n">
         <v>23.6485081020267</v>
       </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
         <v>1.442579323437794</v>
       </c>
-      <c r="M50" t="n">
+      <c r="P50" t="n">
+        <v>5.129919580734308</v>
+      </c>
+      <c r="Q50" t="n">
         <v>2.177011542738722</v>
       </c>
-      <c r="N50" t="n">
+      <c r="R50" t="n">
         <v>3.38202</v>
       </c>
-      <c r="O50" t="n">
+      <c r="S50" t="n">
         <v>0.4890277610497856</v>
       </c>
-      <c r="P50" t="n">
+      <c r="T50" t="n">
+        <v>1.235542998195958</v>
+      </c>
+      <c r="U50" t="n">
         <v>1.18574883380734</v>
       </c>
-      <c r="Q50" t="n">
+      <c r="V50" t="n">
         <v>0.51487</v>
       </c>
     </row>
@@ -4357,45 +5387,60 @@
         <v>0.9315068493150684</v>
       </c>
       <c r="D51" t="n">
+        <v>0.3013698630136986</v>
+      </c>
+      <c r="E51" t="n">
         <v>0.3561643835616438</v>
       </c>
-      <c r="E51" t="n">
+      <c r="F51" t="n">
         <v>0.0073</v>
       </c>
-      <c r="F51" t="n">
+      <c r="G51" t="n">
         <v>0.05109489051094891</v>
       </c>
-      <c r="G51" t="n">
+      <c r="H51" t="n">
+        <v>0.2773722627737226</v>
+      </c>
+      <c r="I51" t="n">
         <v>0.3503649635036497</v>
       </c>
-      <c r="H51" t="n">
+      <c r="J51" t="n">
         <v>0.0073</v>
       </c>
-      <c r="I51" t="n">
+      <c r="K51" t="n">
         <v>7.730364055654995</v>
       </c>
-      <c r="J51" t="n">
+      <c r="L51" t="n">
+        <v>18.30259474120895</v>
+      </c>
+      <c r="M51" t="n">
         <v>17.62778826148003</v>
       </c>
-      <c r="K51" t="n">
+      <c r="N51" t="n">
         <v>19.14312</v>
       </c>
-      <c r="L51" t="n">
+      <c r="O51" t="n">
         <v>1.151746974383665</v>
       </c>
-      <c r="M51" t="n">
+      <c r="P51" t="n">
+        <v>1.901125812384447</v>
+      </c>
+      <c r="Q51" t="n">
         <v>1.408048536354015</v>
       </c>
-      <c r="N51" t="n">
+      <c r="R51" t="n">
         <v>1.21622</v>
       </c>
-      <c r="O51" t="n">
+      <c r="S51" t="n">
         <v>1.086231664937638</v>
       </c>
-      <c r="P51" t="n">
+      <c r="T51" t="n">
+        <v>1.048414119360845</v>
+      </c>
+      <c r="U51" t="n">
         <v>1.069449051715085</v>
       </c>
-      <c r="Q51" t="n">
+      <c r="V51" t="n">
         <v>1.09294</v>
       </c>
     </row>
